--- a/data/trans_bre/P6905-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 21,3</t>
+          <t>-15,82; 21,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 31,0</t>
+          <t>-7,82; 31,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 10,05</t>
+          <t>-34,2; 8,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 24,86</t>
+          <t>-9,47; 25,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 79,98</t>
+          <t>-36,39; 89,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 127,22</t>
+          <t>-17,76; 129,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 37,18</t>
+          <t>-64,6; 25,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 107,39</t>
+          <t>-21,27; 107,45</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,6; 60,46</t>
+          <t>19,73; 63,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 56,91</t>
+          <t>4,76; 56,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 31,86</t>
+          <t>-19,01; 28,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 27,91</t>
+          <t>-6,5; 30,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,13; 386,02</t>
+          <t>48,5; 464,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 332,03</t>
+          <t>14,02; 321,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 162,42</t>
+          <t>-41,54; 138,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 187,79</t>
+          <t>-20,19; 204,6</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 31,17</t>
+          <t>-24,12; 30,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 34,64</t>
+          <t>-5,91; 34,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 69,93</t>
+          <t>-0,62; 68,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 30,99</t>
+          <t>-13,42; 29,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,03; 90,39</t>
+          <t>-54,64; 86,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 200,85</t>
+          <t>-23,31; 212,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 433,72</t>
+          <t>-3,23; 438,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 206,33</t>
+          <t>-52,3; 210,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 37,38</t>
+          <t>3,9; 35,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 25,84</t>
+          <t>-3,43; 24,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 35,0</t>
+          <t>8,49; 35,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 22,56</t>
+          <t>-0,82; 22,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,54; 157,55</t>
+          <t>12,52; 148,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 158,02</t>
+          <t>-13,09; 150,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,66; 194,28</t>
+          <t>28,96; 198,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 174,96</t>
+          <t>-4,59; 167,28</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 14,66</t>
+          <t>-13,13; 14,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 27,84</t>
+          <t>-13,12; 28,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 32,22</t>
+          <t>-1,56; 34,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 25,7</t>
+          <t>-15,9; 24,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 124,79</t>
+          <t>-50,89; 121,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 149,59</t>
+          <t>-31,06; 170,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 173,01</t>
+          <t>-5,84; 184,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 204,58</t>
+          <t>-50,07; 196,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,92</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,0</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,25</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,48</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,52%</t>
         </is>
       </c>
     </row>
@@ -1160,160 +1160,59 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,01; 18,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,79; 22,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,18; 22,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,42; 17,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,28; 67,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,1; 100,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,0; 94,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,03; 89,13</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>10,92</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>15,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14,25</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,48</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36,35%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>52,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>41,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>3,36; 18,85</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6,34; 23,46</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5,94; 22,74</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-2,92; 16,87</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10,35; 70,17</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21,45; 104,06</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>19,03; 96,42</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-6,62; 85,39</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>

--- a/data/trans_bre/P6905-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>-3,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 21,85</t>
+          <t>-14,73; 20,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 31,42</t>
+          <t>-8,2; 30,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 8,66</t>
+          <t>-29,38; 10,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 25,34</t>
+          <t>-22,02; 16,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,39; 89,44</t>
+          <t>-37,79; 79,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 129,08</t>
+          <t>-19,3; 135,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 25,98</t>
+          <t>-59,28; 41,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 107,45</t>
+          <t>-40,07; 49,28</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,15</t>
+          <t>11,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,73; 63,22</t>
+          <t>20,71; 60,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 56,99</t>
+          <t>6,35; 55,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 28,63</t>
+          <t>-18,52; 32,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 30,37</t>
+          <t>-6,2; 28,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,5; 464,59</t>
+          <t>45,6; 395,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,02; 321,35</t>
+          <t>18,95; 318,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 138,64</t>
+          <t>-42,26; 154,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 204,6</t>
+          <t>-20,23; 195,45</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 30,42</t>
+          <t>-24,85; 29,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 34,68</t>
+          <t>-6,98; 34,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 68,06</t>
+          <t>-2,94; 66,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 29,26</t>
+          <t>-14,42; 25,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 86,59</t>
+          <t>-57,14; 83,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 212,54</t>
+          <t>-27,88; 194,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 438,07</t>
+          <t>-11,21; 419,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,3; 210,38</t>
+          <t>-44,28; 164,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,25</t>
+          <t>7,85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 35,07</t>
+          <t>7,08; 37,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 24,51</t>
+          <t>-1,88; 26,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 35,31</t>
+          <t>8,7; 34,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 22,73</t>
+          <t>-4,41; 19,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,52; 148,76</t>
+          <t>23,39; 160,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 150,42</t>
+          <t>-8,32; 177,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,96; 198,17</t>
+          <t>25,28; 190,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 167,28</t>
+          <t>-15,56; 119,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>14,67</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 14,62</t>
+          <t>-13,17; 15,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 28,93</t>
+          <t>-14,47; 29,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 34,15</t>
+          <t>-2,55; 34,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 24,2</t>
+          <t>1,68; 26,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 121,97</t>
+          <t>-49,63; 141,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 170,76</t>
+          <t>-35,1; 148,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 184,91</t>
+          <t>-6,97; 190,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 196,86</t>
+          <t>2,07; 290,55</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>8,38</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 18,75</t>
+          <t>2,9; 19,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 22,76</t>
+          <t>6,83; 24,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 22,52</t>
+          <t>5,42; 22,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 17,0</t>
+          <t>0,73; 14,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,28; 67,27</t>
+          <t>8,99; 71,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,1; 100,31</t>
+          <t>22,47; 105,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,0; 94,61</t>
+          <t>16,84; 95,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 89,13</t>
+          <t>0,84; 69,63</t>
         </is>
       </c>
     </row>
